--- a/docs/validation/V12_Lifecycle_Columns_Current.xlsx
+++ b/docs/validation/V12_Lifecycle_Columns_Current.xlsx
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F128"/>
+  <dimension ref="A1:F129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>Also check that no item with movement is missing its columns. Replace the query with this one and run it:</t>
+          <t>Also check that no item with movement is missing its columns. The query finds items that appear in the fact table, so it cannot skip the very items it is looking for. Replace the query with this one and run it:</t>
         </is>
       </c>
     </row>
@@ -1224,170 +1224,165 @@
     <row r="57" ht="15" customHeight="1">
       <c r="B57" s="19" t="inlineStr">
         <is>
-          <t>FROM   dw.DimItem</t>
+          <t>FROM   dw.DimItem AS i</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="B58" s="19" t="inlineStr">
         <is>
-          <t>WHERE  MonthsActive &gt; 0</t>
+          <t>WHERE  EXISTS (SELECT 1 FROM dw.FactItemMovement AS f WHERE f.ItemKey = i.ItemKey)</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="B59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AND (FirstSeenDateKey IS NULL OR LastSeenDateKey IS NULL OR CohortYear IS NULL);</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="6" customHeight="1"/>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="16" t="n">
+          <t xml:space="preserve">  AND (i.FirstSeenDateKey IS NULL OR i.LastSeenDateKey IS NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="B60" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       OR i.CohortYear IS NULL OR i.MonthsActive IS NULL);</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="6" customHeight="1"/>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="B61" s="14" t="inlineStr">
+      <c r="B62" s="14" t="inlineStr">
         <is>
           <t>Write down ItemsMissingLifecycle.</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="8" customHeight="1"/>
-    <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="5" t="inlineStr">
+    <row r="63" ht="8" customHeight="1"/>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>5. DECIDE: PASS OR FAIL</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="B64" s="14" t="inlineStr">
+    <row r="65" ht="16" customHeight="1">
+      <c r="B65" s="14" t="inlineStr">
         <is>
           <t>Decide against the pass criterion only — it is repeated in At a Glance. Find the row below that matches what you saw.</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="B65" s="6" t="inlineStr">
+    <row r="66" ht="20" customHeight="1">
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>If you see</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>It means</t>
         </is>
       </c>
-      <c r="D65" s="8" t="n"/>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="D66" s="8" t="n"/>
+      <c r="E66" s="6" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="F65" s="8" t="n"/>
-    </row>
-    <row r="66" ht="42" customHeight="1">
-      <c r="B66" s="10" t="inlineStr">
+      <c r="F66" s="8" t="n"/>
+    </row>
+    <row r="67" ht="42" customHeight="1">
+      <c r="B67" s="10" t="inlineStr">
         <is>
           <t>The two months are equal and ItemsMissingLifecycle is 0</t>
         </is>
       </c>
-      <c r="C66" s="10" t="inlineStr">
+      <c r="C67" s="10" t="inlineStr">
         <is>
           <t>The lifecycle columns match the latest load</t>
         </is>
       </c>
-      <c r="D66" s="8" t="n"/>
-      <c r="E66" s="10" t="inlineStr">
+      <c r="D67" s="8" t="n"/>
+      <c r="E67" s="10" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="F66" s="8" t="n"/>
-    </row>
-    <row r="67" ht="42" customHeight="1">
-      <c r="B67" s="12" t="inlineStr">
+      <c r="F67" s="8" t="n"/>
+    </row>
+    <row r="68" ht="42" customHeight="1">
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>LastSeenInDimItem is earlier than LastMonthInFact</t>
         </is>
       </c>
-      <c r="C67" s="12" t="inlineStr">
+      <c r="C68" s="12" t="inlineStr">
         <is>
           <t>New data was loaded but sql/06 was not re-run</t>
         </is>
       </c>
-      <c r="D67" s="8" t="n"/>
-      <c r="E67" s="12" t="inlineStr">
+      <c r="D68" s="8" t="n"/>
+      <c r="E68" s="12" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="F67" s="8" t="n"/>
-    </row>
-    <row r="68" ht="28" customHeight="1">
-      <c r="B68" s="10" t="inlineStr">
+      <c r="F68" s="8" t="n"/>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="B69" s="10" t="inlineStr">
         <is>
           <t>ItemsMissingLifecycle is more than 0</t>
         </is>
       </c>
-      <c r="C68" s="10" t="inlineStr">
+      <c r="C69" s="10" t="inlineStr">
         <is>
           <t>sql/06 did not finish, or new items arrived after it ran</t>
         </is>
       </c>
-      <c r="D68" s="8" t="n"/>
-      <c r="E68" s="10" t="inlineStr">
+      <c r="D69" s="8" t="n"/>
+      <c r="E69" s="10" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="F68" s="8" t="n"/>
-    </row>
-    <row r="69" ht="8" customHeight="1"/>
-    <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="5" t="inlineStr">
+      <c r="F69" s="8" t="n"/>
+    </row>
+    <row r="70" ht="8" customHeight="1"/>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>6. RECORD THE RESULT</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="B71" s="13" t="inlineStr">
+    <row r="72" ht="20" customHeight="1">
+      <c r="B72" s="13" t="inlineStr">
         <is>
           <t>6.1 In document 22</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B72" s="14" t="inlineStr">
-        <is>
-          <t>Open X:\retail-sector-health\docs\22_Validation_Results.xlsx in Excel.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>Open X:\retail-sector-health\docs\22_Validation_Results.xlsx in Excel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B73" s="14" t="inlineStr">
+      <c r="B74" s="14" t="inlineStr">
         <is>
           <t>Select the Run Summary tab. Find the row for this run.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="29" customHeight="1">
-      <c r="B74" s="17" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C74" s="14" t="inlineStr">
-        <is>
-          <t>If you are checking during the first build, the run is Run 1. If Run 1 is not there yet, type Run 1 in the first empty Run ID cell.</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1394,7 @@
       </c>
       <c r="C75" s="14" t="inlineStr">
         <is>
-          <t>Fill in Date, Trigger (choose from the drop-down: Initial build for the first build), Model / commit reference and Run by.</t>
+          <t>If you are checking during the first build, the run is Run 1. If Run 1 is not there yet, type Run 1 in the first empty Run ID cell.</t>
         </is>
       </c>
     </row>
@@ -1411,59 +1406,59 @@
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
+          <t>Fill in Date, Trigger (choose from the drop-down: Initial build for the first build), Model / commit reference and Run by.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="29" customHeight="1">
+      <c r="B77" s="17" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C77" s="14" t="inlineStr">
+        <is>
           <t>For Model / commit reference, open PowerShell, run the command below, and type the seven characters it prints.</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="B77" s="17" t="inlineStr">
+    <row r="78" ht="16" customHeight="1">
+      <c r="B78" s="17" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C77" s="14" t="inlineStr">
+      <c r="C78" s="14" t="inlineStr">
         <is>
           <t>Do not type in the columns from Checks recorded to Outcome. They are formulas and fill themselves in.</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="15" customHeight="1">
-      <c r="B78" s="19" t="inlineStr">
+    <row r="79" ht="15" customHeight="1">
+      <c r="B79" s="19" t="inlineStr">
         <is>
           <t>git -C X:\retail-sector-health log -1 --format=%h</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="6" customHeight="1"/>
-    <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B80" s="14" t="inlineStr">
-        <is>
-          <t>Select the Check Results tab. Find the row whose Run ID is this run and whose # is 12.</t>
-        </is>
-      </c>
-    </row>
+    <row r="80" ht="6" customHeight="1"/>
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>Select the Check Results tab. Find the row whose Run ID is this run and whose # is 12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="16" customHeight="1">
+      <c r="A82" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B81" s="14" t="inlineStr">
+      <c r="B82" s="14" t="inlineStr">
         <is>
           <t>Fill in four cells on that row:</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="16" customHeight="1">
-      <c r="B82" s="17" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C82" s="14" t="inlineStr">
-        <is>
-          <t>Result: choose Pass, Fail or N/A from the drop-down.</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1470,7 @@
       </c>
       <c r="C83" s="14" t="inlineStr">
         <is>
-          <t>Observed value / evidence: the numbers you saw — see the examples below. Never just ‘ok’.</t>
+          <t>Result: choose Pass, Fail or N/A from the drop-down.</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1482,7 @@
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>Checked by: your name or initials.</t>
+          <t>Observed value / evidence: the numbers you saw — see the examples below. Never just ‘ok’.</t>
         </is>
       </c>
     </row>
@@ -1499,123 +1494,120 @@
       </c>
       <c r="C85" s="14" t="inlineStr">
         <is>
+          <t>Checked by: your name or initials.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C86" s="14" t="inlineStr">
+        <is>
           <t>Date checked: today’s date.</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="16" customHeight="1">
-      <c r="A86" s="16" t="n">
+    <row r="87" ht="16" customHeight="1">
+      <c r="A87" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B86" s="14" t="inlineStr">
+      <c r="B87" s="14" t="inlineStr">
         <is>
           <t>Save the workbook. Go back to Run Summary: Checks recorded has gone up by one.</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="B87" s="6" t="inlineStr">
+    <row r="88" ht="20" customHeight="1">
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>Situation</t>
         </is>
       </c>
-      <c r="C87" s="6" t="inlineStr">
+      <c r="C88" s="6" t="inlineStr">
         <is>
           <t>Write this in Observed value / evidence</t>
-        </is>
-      </c>
-      <c r="D87" s="7" t="n"/>
-      <c r="E87" s="7" t="n"/>
-      <c r="F87" s="8" t="n"/>
-    </row>
-    <row r="88" ht="16" customHeight="1">
-      <c r="B88" s="10" t="inlineStr">
-        <is>
-          <t>Example of a pass</t>
-        </is>
-      </c>
-      <c r="C88" s="10" t="inlineStr">
-        <is>
-          <t>Last seen in DimItem 20260701 · last month in fact 20260701 · 0 items missing lifecycle</t>
         </is>
       </c>
       <c r="D88" s="7" t="n"/>
       <c r="E88" s="7" t="n"/>
       <c r="F88" s="8" t="n"/>
     </row>
-    <row r="89" ht="28" customHeight="1">
-      <c r="B89" s="12" t="inlineStr">
-        <is>
-          <t>Example of another result</t>
-        </is>
-      </c>
-      <c r="C89" s="12" t="inlineStr">
-        <is>
-          <t>Last seen 20260601 · fact 20260701 — sql/06 not re-run after the July load</t>
+    <row r="89" ht="16" customHeight="1">
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>Example of a pass</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>Last seen in DimItem 20260701 · last month in fact 20260701 · 0 items missing lifecycle</t>
         </is>
       </c>
       <c r="D89" s="7" t="n"/>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="8" t="n"/>
     </row>
-    <row r="90" ht="16" customHeight="1">
-      <c r="B90" s="20" t="inlineStr">
+    <row r="90" ht="28" customHeight="1">
+      <c r="B90" s="12" t="inlineStr">
+        <is>
+          <t>Example of another result</t>
+        </is>
+      </c>
+      <c r="C90" s="12" t="inlineStr">
+        <is>
+          <t>Last seen 20260601 · fact 20260701 — sql/06 not re-run after the July load</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="n"/>
+      <c r="E90" s="7" t="n"/>
+      <c r="F90" s="8" t="n"/>
+    </row>
+    <row r="91" ht="16" customHeight="1">
+      <c r="B91" s="20" t="inlineStr">
         <is>
           <t>Examples show the wording and level of detail to aim for. The numbers in them are illustrations, not expected values.</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="B91" s="13" t="inlineStr">
+    <row r="92" ht="20" customHeight="1">
+      <c r="B92" s="13" t="inlineStr">
         <is>
           <t>6.2 In document 26</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="16" t="n">
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B92" s="14" t="inlineStr">
+      <c r="B93" s="14" t="inlineStr">
         <is>
           <t>Open X:\retail-sector-health\docs\26_Validation_Timing_Checklist.xlsx and select the Build Checklist tab.</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="29" customHeight="1">
-      <c r="A93" s="16" t="n">
+    <row r="94" ht="29" customHeight="1">
+      <c r="A94" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B93" s="14" t="inlineStr">
+      <c r="B94" s="14" t="inlineStr">
         <is>
           <t>Find the row with the Ref shown below that matches where you are in the build. Set Result to the same result, and fill Date, Checked by and Observed value the same way.</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="B94" s="6" t="inlineStr">
+    <row r="95" ht="20" customHeight="1">
+      <c r="B95" s="6" t="inlineStr">
         <is>
           <t>Ref in doc 26</t>
         </is>
       </c>
-      <c r="C94" s="6" t="inlineStr">
+      <c r="C95" s="6" t="inlineStr">
         <is>
           <t>When it applies</t>
-        </is>
-      </c>
-      <c r="D94" s="7" t="n"/>
-      <c r="E94" s="7" t="n"/>
-      <c r="F94" s="8" t="n"/>
-    </row>
-    <row r="95" ht="16" customHeight="1">
-      <c r="B95" s="10" t="inlineStr">
-        <is>
-          <t>G1.06</t>
-        </is>
-      </c>
-      <c r="C95" s="10" t="inlineStr">
-        <is>
-          <t>First build, right after sql/06</t>
         </is>
       </c>
       <c r="D95" s="7" t="n"/>
@@ -1623,128 +1615,131 @@
       <c r="F95" s="8" t="n"/>
     </row>
     <row r="96" ht="16" customHeight="1">
-      <c r="B96" s="12" t="inlineStr">
-        <is>
-          <t>G5.10</t>
-        </is>
-      </c>
-      <c r="C96" s="12" t="inlineStr">
-        <is>
-          <t>The model pass</t>
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>G1.06</t>
+        </is>
+      </c>
+      <c r="C96" s="10" t="inlineStr">
+        <is>
+          <t>First build, right after sql/06</t>
         </is>
       </c>
       <c r="D96" s="7" t="n"/>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="8" t="n"/>
     </row>
-    <row r="97" ht="8" customHeight="1"/>
-    <row r="98" ht="22" customHeight="1">
-      <c r="A98" s="5" t="inlineStr">
+    <row r="97" ht="16" customHeight="1">
+      <c r="B97" s="12" t="inlineStr">
+        <is>
+          <t>G5.10</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>The model pass</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="n"/>
+      <c r="E97" s="7" t="n"/>
+      <c r="F97" s="8" t="n"/>
+    </row>
+    <row r="98" ht="8" customHeight="1"/>
+    <row r="99" ht="22" customHeight="1">
+      <c r="A99" s="5" t="inlineStr">
         <is>
           <t>7. IF IT FAILS</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="B99" s="13" t="inlineStr">
+    <row r="100" ht="20" customHeight="1">
+      <c r="B100" s="13" t="inlineStr">
         <is>
           <t>7.1 What usually causes it</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="B100" s="6" t="inlineStr">
+    <row r="101" ht="20" customHeight="1">
+      <c r="B101" s="6" t="inlineStr">
         <is>
           <t>What you see</t>
         </is>
       </c>
-      <c r="C100" s="6" t="inlineStr">
+      <c r="C101" s="6" t="inlineStr">
         <is>
           <t>Likely cause</t>
         </is>
       </c>
-      <c r="D100" s="8" t="n"/>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="D101" s="8" t="n"/>
+      <c r="E101" s="6" t="inlineStr">
         <is>
           <t>What to do</t>
         </is>
       </c>
-      <c r="F100" s="8" t="n"/>
-    </row>
-    <row r="101" ht="16" customHeight="1">
-      <c r="B101" s="10" t="inlineStr">
+      <c r="F101" s="8" t="n"/>
+    </row>
+    <row r="102" ht="16" customHeight="1">
+      <c r="B102" s="10" t="inlineStr">
         <is>
           <t>Months differ</t>
         </is>
       </c>
-      <c r="C101" s="10" t="inlineStr">
+      <c r="C102" s="10" t="inlineStr">
         <is>
           <t>sql/06 not re-run after a reload</t>
         </is>
       </c>
-      <c r="D101" s="8" t="n"/>
-      <c r="E101" s="10" t="inlineStr">
+      <c r="D102" s="8" t="n"/>
+      <c r="E102" s="10" t="inlineStr">
         <is>
           <t>Run sql/06, then run this check again</t>
         </is>
       </c>
-      <c r="F101" s="8" t="n"/>
-    </row>
-    <row r="102" ht="16" customHeight="1">
-      <c r="B102" s="12" t="inlineStr">
+      <c r="F102" s="8" t="n"/>
+    </row>
+    <row r="103" ht="16" customHeight="1">
+      <c r="B103" s="12" t="inlineStr">
         <is>
           <t>Items missing lifecycle</t>
         </is>
       </c>
-      <c r="C102" s="12" t="inlineStr">
+      <c r="C103" s="12" t="inlineStr">
         <is>
           <t>sql/06 stopped part-way, or ran before sql/05 finished</t>
         </is>
       </c>
-      <c r="D102" s="8" t="n"/>
-      <c r="E102" s="12" t="inlineStr">
+      <c r="D103" s="8" t="n"/>
+      <c r="E103" s="12" t="inlineStr">
         <is>
           <t>Run sql/05 then sql/06 in order</t>
         </is>
       </c>
-      <c r="F102" s="8" t="n"/>
-    </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="B103" s="13" t="inlineStr">
+      <c r="F103" s="8" t="n"/>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="B104" s="13" t="inlineStr">
         <is>
           <t>7.2 Record the failure</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="29" customHeight="1">
-      <c r="A104" s="16" t="n">
+    <row r="105" ht="29" customHeight="1">
+      <c r="A105" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B104" s="14" t="inlineStr">
+      <c r="B105" s="14" t="inlineStr">
         <is>
           <t>On the Check Results tab of document 22, set Result to Fail for check 12. Write the numbers you saw in Observed value. Do not change it to N/A and do not clear it.</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="16" customHeight="1">
-      <c r="A105" s="16" t="n">
+    <row r="106" ht="16" customHeight="1">
+      <c r="A106" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B105" s="14" t="inlineStr">
+      <c r="B106" s="14" t="inlineStr">
         <is>
           <t>Select the Failure Log tab and fill the first empty row:</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="16" customHeight="1">
-      <c r="B106" s="17" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C106" s="14" t="inlineStr">
-        <is>
-          <t>Failure ID: the next number — F-001, then F-002 and so on.</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1751,7 @@
       </c>
       <c r="C107" s="14" t="inlineStr">
         <is>
-          <t>Run ID and Check #: this run and check number.</t>
+          <t>Failure ID: the next number — F-001, then F-002 and so on.</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1763,7 @@
       </c>
       <c r="C108" s="14" t="inlineStr">
         <is>
-          <t>What was observed: the same numbers.</t>
+          <t>Run ID and Check #: this run and check number.</t>
         </is>
       </c>
     </row>
@@ -1780,57 +1775,57 @@
       </c>
       <c r="C109" s="14" t="inlineStr">
         <is>
+          <t>What was observed: the same numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="16" customHeight="1">
+      <c r="B110" s="17" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C110" s="14" t="inlineStr">
+        <is>
           <t>Root cause: what you found, or ‘not yet known’.</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="16" customHeight="1">
-      <c r="A110" s="16" t="n">
+    <row r="111" ht="16" customHeight="1">
+      <c r="A111" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B110" s="14" t="inlineStr">
+      <c r="B111" s="14" t="inlineStr">
         <is>
           <t>Fix the cause. Then fill Fix applied, Fixed by and Date fixed. Status changes by itself to ‘Fix applied — not re-verified’.</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="29" customHeight="1">
-      <c r="A111" s="16" t="n">
+    <row r="112" ht="29" customHeight="1">
+      <c r="A112" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B111" s="14" t="inlineStr">
+      <c r="B112" s="14" t="inlineStr">
         <is>
           <t>Run the whole procedure again as a new run — on Run Summary add Run 2 with Trigger Ad hoc and name the fix in Notes. Record the new result against Run 2.</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="16" customHeight="1">
-      <c r="A112" s="16" t="n">
+    <row r="113" ht="16" customHeight="1">
+      <c r="A113" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B112" s="14" t="inlineStr">
+      <c r="B113" s="14" t="inlineStr">
         <is>
           <t>When it passes, type Run 2 in Re-verified in run on the Failure Log. Status changes to ‘Closed — re-verified’.</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="8" customHeight="1"/>
-    <row r="114" ht="22" customHeight="1">
-      <c r="A114" s="5" t="inlineStr">
+    <row r="114" ht="8" customHeight="1"/>
+    <row r="115" ht="22" customHeight="1">
+      <c r="A115" s="5" t="inlineStr">
         <is>
           <t>8. WHEN TO RUN IT AGAIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="16" customHeight="1">
-      <c r="A115" s="15" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B115" s="14" t="inlineStr">
-        <is>
-          <t>At the model pass (gate G5).</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1837,7 @@
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>After every reload of the county data — sql/06 first, then this check.</t>
+          <t>At the model pass (gate G5).</t>
         </is>
       </c>
     </row>
@@ -1854,27 +1849,27 @@
       </c>
       <c r="B117" s="14" t="inlineStr">
         <is>
+          <t>After every reload of the county data — sql/06 first, then this check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="16" customHeight="1">
+      <c r="A118" s="15" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B118" s="14" t="inlineStr">
+        <is>
           <t>Document 25 §4 lists this among the twelve data checks.</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="8" customHeight="1"/>
-    <row r="119" ht="22" customHeight="1">
-      <c r="A119" s="5" t="inlineStr">
+    <row r="119" ht="8" customHeight="1"/>
+    <row r="120" ht="22" customHeight="1">
+      <c r="A120" s="5" t="inlineStr">
         <is>
           <t>9. REFERENCES</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="16" customHeight="1">
-      <c r="A120" s="15" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B120" s="14" t="inlineStr">
-        <is>
-          <t>Document 02 §9 — the seventeen checks and their pass criteria.</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1881,7 @@
       </c>
       <c r="B121" s="14" t="inlineStr">
         <is>
-          <t>Document 22, Check Catalog tab — what this check protects against and where it runs.</t>
+          <t>Document 02 §9 — the seventeen checks and their pass criteria.</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1893,7 @@
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>Document 25 — when each check is run, and when to re-run it.</t>
+          <t>Document 22, Check Catalog tab — what this check protects against and where it runs.</t>
         </is>
       </c>
     </row>
@@ -1910,74 +1905,89 @@
       </c>
       <c r="B123" s="14" t="inlineStr">
         <is>
+          <t>Document 25 — when each check is run, and when to re-run it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="16" customHeight="1">
+      <c r="A124" s="15" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B124" s="14" t="inlineStr">
+        <is>
           <t>Document 26 — the gate rows this check is ticked against.</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="18" customHeight="1">
-      <c r="B124" s="21" t="inlineStr">
+    <row r="125" ht="18" customHeight="1">
+      <c r="B125" s="21" t="inlineStr">
         <is>
           <t>Connect with SQL Server Management Studio</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="8" customHeight="1"/>
-    <row r="126" ht="22" customHeight="1">
-      <c r="A126" s="5" t="inlineStr">
+    <row r="126" ht="8" customHeight="1"/>
+    <row r="127" ht="22" customHeight="1">
+      <c r="A127" s="5" t="inlineStr">
         <is>
           <t>10. AI ASSISTANCE DISCLOSURE</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="29" customHeight="1">
-      <c r="B127" s="14" t="inlineStr">
+    <row r="128" ht="29" customHeight="1">
+      <c r="B128" s="14" t="inlineStr">
         <is>
           <t>Portions of this procedure were drafted with the assistance of a generative AI system. The author defined the project and its validation approach and reviewed all content before publication.</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="43.5" customHeight="1">
-      <c r="B128" s="14" t="inlineStr">
+    <row r="129" ht="43.5" customHeight="1">
+      <c r="B129" s="14" t="inlineStr">
         <is>
           <t>The pass criterion is quoted from document 02 §9. Queries use only tables, columns and measures defined in documents 02 and 20, and the visual numbers come from the document 15 specification tables. Tool steps were checked against Microsoft Learn; where a screen label varies by version, the procedure says so.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="122">
+  <mergeCells count="123">
+    <mergeCell ref="B106:F106"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B16:F16"/>
     <mergeCell ref="C39:F39"/>
-    <mergeCell ref="B16:F16"/>
     <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B122:F122"/>
-    <mergeCell ref="B71:F71"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="B58:F58"/>
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C87:F87"/>
+    <mergeCell ref="C78:F78"/>
+    <mergeCell ref="B60:F60"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C107:F107"/>
     <mergeCell ref="C89:F89"/>
-    <mergeCell ref="E65:F65"/>
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="C88:F88"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="B37:F37"/>
+    <mergeCell ref="C41:F41"/>
     <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C41:F41"/>
     <mergeCell ref="E101:F101"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="B118:F118"/>
     <mergeCell ref="B92:F92"/>
-    <mergeCell ref="E100:F100"/>
+    <mergeCell ref="C67:D67"/>
     <mergeCell ref="B20:F20"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="A70:F70"/>
-    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B94:F94"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="E102:F102"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="A99:F99"/>
     <mergeCell ref="B54:F54"/>
+    <mergeCell ref="B125:F125"/>
     <mergeCell ref="B72:F72"/>
     <mergeCell ref="E67:F67"/>
     <mergeCell ref="B121:F121"/>
@@ -1986,85 +1996,83 @@
     <mergeCell ref="B105:F105"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B111:F111"/>
     <mergeCell ref="C96:F96"/>
     <mergeCell ref="C83:F83"/>
-    <mergeCell ref="B111:F111"/>
-    <mergeCell ref="B120:F120"/>
-    <mergeCell ref="A126:F126"/>
     <mergeCell ref="A35:F35"/>
     <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B57:F57"/>
     <mergeCell ref="C14:F14"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B99:F99"/>
+    <mergeCell ref="B82:F82"/>
+    <mergeCell ref="A127:F127"/>
     <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A114:F114"/>
+    <mergeCell ref="B74:F74"/>
     <mergeCell ref="C40:F40"/>
-    <mergeCell ref="A98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="C90:F90"/>
     <mergeCell ref="C66:D66"/>
     <mergeCell ref="B45:F45"/>
     <mergeCell ref="E66:F66"/>
     <mergeCell ref="C102:D102"/>
     <mergeCell ref="C76:F76"/>
+    <mergeCell ref="C110:F110"/>
+    <mergeCell ref="B47:F47"/>
     <mergeCell ref="C68:D68"/>
-    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="E68:F68"/>
     <mergeCell ref="C8:F8"/>
-    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="B62:F62"/>
     <mergeCell ref="B59:F59"/>
-    <mergeCell ref="C82:F82"/>
     <mergeCell ref="B31:F31"/>
     <mergeCell ref="B46:F46"/>
-    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="A71:F71"/>
     <mergeCell ref="B48:F48"/>
-    <mergeCell ref="C65:D65"/>
     <mergeCell ref="C77:F77"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="C86:F86"/>
     <mergeCell ref="C108:F108"/>
-    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="E69:F69"/>
     <mergeCell ref="B73:F73"/>
+    <mergeCell ref="A115:F115"/>
+    <mergeCell ref="B87:F87"/>
+    <mergeCell ref="C97:F97"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="B128:F128"/>
-    <mergeCell ref="C94:F94"/>
     <mergeCell ref="C109:F109"/>
     <mergeCell ref="C84:F84"/>
     <mergeCell ref="C22:F22"/>
+    <mergeCell ref="B65:F65"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C95:F95"/>
     <mergeCell ref="B123:F123"/>
     <mergeCell ref="B36:F36"/>
-    <mergeCell ref="C95:F95"/>
     <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B110:F110"/>
     <mergeCell ref="C101:D101"/>
+    <mergeCell ref="B113:F113"/>
     <mergeCell ref="B91:F91"/>
     <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C106:F106"/>
+    <mergeCell ref="B100:F100"/>
+    <mergeCell ref="A120:F120"/>
     <mergeCell ref="C7:F7"/>
-    <mergeCell ref="B115:F115"/>
     <mergeCell ref="B93:F93"/>
-    <mergeCell ref="B86:F86"/>
     <mergeCell ref="B117:F117"/>
-    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="C103:D103"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="C42:F42"/>
-    <mergeCell ref="C74:F74"/>
     <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B103:F103"/>
-    <mergeCell ref="B78:F78"/>
     <mergeCell ref="B112:F112"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="C85:F85"/>
-    <mergeCell ref="B127:F127"/>
     <mergeCell ref="B49:F49"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="C75:F75"/>
-    <mergeCell ref="B64:F64"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="B104:F104"/>
     <mergeCell ref="B51:F51"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A119:F119"/>
+    <mergeCell ref="B79:F79"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="B32:F32"/>
   </mergeCells>
